--- a/data/Авлагын эхний үлдэгдэл.xlsx
+++ b/data/Авлагын эхний үлдэгдэл.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\PN тооцоо\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F76E31D-2D89-4ED8-8906-A613C256DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -22,9 +28,6 @@
     <t>Харилцагчийн нэр</t>
   </si>
   <si>
-    <t>Эцсийн үлдэгдэл</t>
-  </si>
-  <si>
     <t>6390994</t>
   </si>
   <si>
@@ -983,13 +986,15 @@
   </si>
   <si>
     <t>Star fitness /Од/</t>
+  </si>
+  <si>
+    <t>Эхний үлдэгдэл</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1021,7 +1026,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe0d6d3"/>
+        <fgColor rgb="FFE0D6D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -1035,55 +1040,55 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </left>
       <right style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </right>
       <top style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </left>
       <right style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FFbdb1b7"/>
+        <color rgb="FFBDB1B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1091,50 +1096,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1145,10 +1150,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1186,71 +1191,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1278,7 +1283,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1301,11 +1306,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1314,13 +1319,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1330,7 +1335,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1339,7 +1344,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1348,7 +1353,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1356,10 +1361,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1424,21 +1429,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="29.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="11.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="11.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="29.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1446,17 +1451,17 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="8">
         <v>6283878.5</v>
@@ -1464,12 +1469,12 @@
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="8">
         <v>1983150</v>
@@ -1477,12 +1482,12 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="8">
         <v>791080</v>
@@ -1490,12 +1495,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>390200</v>
@@ -1503,12 +1508,12 @@
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="8">
         <v>3032760</v>
@@ -1516,12 +1521,12 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="C7" s="8">
         <v>565040</v>
@@ -1529,12 +1534,12 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="C8" s="8">
         <v>1229336</v>
@@ -1542,25 +1547,25 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" s="8">
-        <v>8523633.7</v>
+        <v>8523633.6999999993</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="C10" s="8">
         <v>-106180.74</v>
@@ -1568,12 +1573,12 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="C11" s="8">
         <v>249850</v>
@@ -1581,12 +1586,12 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="C12" s="8">
         <v>10097283.32</v>
@@ -1594,38 +1599,38 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="C13" s="8">
-        <v>232326238.99</v>
+        <v>232326238.99000001</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="C14" s="8">
-        <v>-81654.71</v>
+        <v>-81654.710000000006</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="C15" s="8">
         <v>1540000</v>
@@ -1633,12 +1638,12 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="16" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="C16" s="8">
         <v>37000</v>
@@ -1646,12 +1651,12 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="17" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="C17" s="8">
         <v>22950</v>
@@ -1659,12 +1664,12 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="18" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C18" s="8">
         <v>2003635</v>
@@ -1672,12 +1677,12 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="C19" s="8">
         <v>1054519.31</v>
@@ -1685,25 +1690,25 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="20" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="C20" s="8">
-        <v>8043383.35</v>
+        <v>8043383.3499999996</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="21" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="C21" s="8">
         <v>534240</v>
@@ -1711,12 +1716,12 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="22" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="C22" s="8">
         <v>11761091</v>
@@ -1724,12 +1729,12 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="23" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="C23" s="8">
         <v>1359600</v>
@@ -1737,12 +1742,12 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="24" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="C24" s="8">
         <v>500000</v>
@@ -1750,25 +1755,25 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="25" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="C25" s="8">
-        <v>10497242.39</v>
+        <v>10497242.390000001</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="26" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="C26" s="8">
         <v>372200</v>
@@ -1776,12 +1781,12 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="27" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="C27" s="8">
         <v>256500</v>
@@ -1789,12 +1794,12 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="28" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="C28" s="8">
         <v>3053819</v>
@@ -1802,12 +1807,12 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="29" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="C29" s="8">
         <v>39335</v>
@@ -1815,12 +1820,12 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="30" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="C30" s="8">
         <v>635335.36</v>
@@ -1828,12 +1833,12 @@
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="31" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="C31" s="8">
         <v>1933670</v>
@@ -1841,12 +1846,12 @@
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="32" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="C32" s="8">
         <v>900000</v>
@@ -1854,12 +1859,12 @@
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="33" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="C33" s="8">
         <v>105600</v>
@@ -1867,12 +1872,12 @@
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="34" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="C34" s="8">
         <v>103500</v>
@@ -1880,12 +1885,12 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="35" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="C35" s="8">
         <v>549000</v>
@@ -1893,12 +1898,12 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="36" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="C36" s="8">
         <v>5199160</v>
@@ -1906,12 +1911,12 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="37" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="C37" s="8">
         <v>6380780</v>
@@ -1919,12 +1924,12 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="38" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="C38" s="8">
         <v>363000</v>
@@ -1932,25 +1937,25 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="39" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="C39" s="8">
-        <v>9438449.29</v>
+        <v>9438449.2899999991</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="40" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="C40" s="8">
         <v>1095500</v>
@@ -1958,12 +1963,12 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="41" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="C41" s="8">
         <v>667200</v>
@@ -1971,12 +1976,12 @@
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="42" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="C42" s="8">
         <v>2143090</v>
@@ -1984,12 +1989,12 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="43" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="C43" s="8">
         <v>762000</v>
@@ -1997,12 +2002,12 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="24" customFormat="1" s="1">
+    <row r="44" spans="1:5" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="C44" s="8">
         <v>1267520</v>
@@ -2010,12 +2015,12 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="24" customFormat="1" s="1">
+    <row r="45" spans="1:5" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="C45" s="8">
         <v>2266650</v>
@@ -2023,12 +2028,12 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="24" customFormat="1" s="1">
+    <row r="46" spans="1:5" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="C46" s="8">
         <v>785200</v>
@@ -2036,12 +2041,12 @@
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="47" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="C47" s="8">
         <v>1715500</v>
@@ -2049,12 +2054,12 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="48" spans="1:5" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="C48" s="8">
         <v>2524000</v>
@@ -2062,25 +2067,25 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="49" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="C49" s="8">
-        <v>34524763.39</v>
+        <v>34524763.390000001</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="50" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="C50" s="8">
         <v>90000</v>
@@ -2088,12 +2093,12 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="51" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="C51" s="8">
         <v>1336900</v>
@@ -2101,12 +2106,12 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="52" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="C52" s="8">
         <v>716150</v>
@@ -2114,12 +2119,12 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="53" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="C53" s="8">
         <v>497350</v>
@@ -2127,12 +2132,12 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="54" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="C54" s="8">
         <v>2357920</v>
@@ -2140,12 +2145,12 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="55" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="C55" s="8">
         <v>918850</v>
@@ -2153,12 +2158,12 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="56" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="C56" s="8">
         <v>810600</v>
@@ -2166,12 +2171,12 @@
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="57" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="C57" s="8">
         <v>3453600</v>
@@ -2179,12 +2184,12 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="58" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="C58" s="8">
         <v>2228300</v>
@@ -2192,12 +2197,12 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="59" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="C59" s="8">
         <v>192510</v>
@@ -2205,12 +2210,12 @@
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="60" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>117</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>118</v>
       </c>
       <c r="C60" s="8">
         <v>620000</v>
@@ -2218,12 +2223,12 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="61" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="C61" s="8">
         <v>204680</v>
@@ -2231,12 +2236,12 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="62" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="C62" s="8">
         <v>1235520</v>
@@ -2244,12 +2249,12 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="63" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="C63" s="8">
         <v>56940</v>
@@ -2257,12 +2262,12 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="64" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="C64" s="8">
         <v>208000</v>
@@ -2270,12 +2275,12 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="65" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>128</v>
       </c>
       <c r="C65" s="8">
         <v>1632020</v>
@@ -2283,12 +2288,12 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="66" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="C66" s="8">
         <v>232000</v>
@@ -2296,12 +2301,12 @@
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="67" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="C67" s="8">
         <v>2253055</v>
@@ -2309,12 +2314,12 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="68" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>134</v>
       </c>
       <c r="C68" s="8">
         <v>400000</v>
@@ -2322,12 +2327,12 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="15" customFormat="1" s="1">
+    <row r="69" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="C69" s="8">
         <v>925500</v>
@@ -2335,12 +2340,12 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="70" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>138</v>
       </c>
       <c r="C70" s="8">
         <v>630000</v>
@@ -2348,12 +2353,12 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="71" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="C71" s="8">
         <v>885520</v>
@@ -2361,12 +2366,12 @@
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="72" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="C72" s="8">
         <v>2548000</v>
@@ -2374,12 +2379,12 @@
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="73" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="C73" s="8">
         <v>3041420</v>
@@ -2387,12 +2392,12 @@
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="74" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="C74" s="8">
         <v>108000</v>
@@ -2400,12 +2405,12 @@
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="75" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>148</v>
       </c>
       <c r="C75" s="8">
         <v>800</v>
@@ -2413,12 +2418,12 @@
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="76" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="C76" s="8">
         <v>975000</v>
@@ -2426,12 +2431,12 @@
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="77" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="C77" s="8">
         <v>812000</v>
@@ -2439,12 +2444,12 @@
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="78" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="C78" s="8">
         <v>-8</v>
@@ -2452,12 +2457,12 @@
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="79" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>156</v>
       </c>
       <c r="C79" s="8">
         <v>475200</v>
@@ -2465,12 +2470,12 @@
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="80" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="C80" s="8">
         <v>213840</v>
@@ -2478,12 +2483,12 @@
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="81" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="C81" s="8">
         <v>410400</v>
@@ -2491,12 +2496,12 @@
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="82" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>161</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>162</v>
       </c>
       <c r="C82" s="8">
         <v>6313500</v>
@@ -2504,12 +2509,12 @@
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="83" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>164</v>
       </c>
       <c r="C83" s="8">
         <v>4585480</v>
@@ -2517,12 +2522,12 @@
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="84" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>166</v>
       </c>
       <c r="C84" s="8">
         <v>106000</v>
@@ -2530,12 +2535,12 @@
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="85" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="C85" s="8">
         <v>1565400.29</v>
@@ -2543,12 +2548,12 @@
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="86" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>170</v>
       </c>
       <c r="C86" s="8">
         <v>344790</v>
@@ -2556,12 +2561,12 @@
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="87" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="C87" s="8">
         <v>805524</v>
@@ -2569,12 +2574,12 @@
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="88" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>174</v>
       </c>
       <c r="C88" s="8">
         <v>400500</v>
@@ -2582,12 +2587,12 @@
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="89" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="C89" s="8">
         <v>2571520</v>
@@ -2595,12 +2600,12 @@
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="90" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="C90" s="8">
         <v>180000</v>
@@ -2608,12 +2613,12 @@
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="91" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="C91" s="8">
         <v>1235520</v>
@@ -2621,12 +2626,12 @@
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="92" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B92" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="C92" s="8">
         <v>6679900</v>
@@ -2634,12 +2639,12 @@
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="15" customFormat="1" s="1">
+    <row r="93" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>184</v>
       </c>
       <c r="C93" s="8">
         <v>106920</v>
@@ -2647,12 +2652,12 @@
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="94" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="C94" s="8">
         <v>1272000</v>
@@ -2660,51 +2665,51 @@
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="95" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B95" s="7" t="s">
-        <v>188</v>
-      </c>
       <c r="C95" s="8">
-        <v>53159619.72</v>
+        <v>53159619.719999999</v>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="96" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>190</v>
-      </c>
       <c r="C96" s="8">
-        <v>76106491.9</v>
+        <v>76106491.900000006</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="97" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="C97" s="8">
-        <v>99102807.89</v>
+        <v>99102807.890000001</v>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="98" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>194</v>
       </c>
       <c r="C98" s="8">
         <v>13808626.27</v>
@@ -2712,12 +2717,12 @@
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="99" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>195</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>196</v>
       </c>
       <c r="C99" s="8">
         <v>223809.3</v>
@@ -2725,12 +2730,12 @@
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="100" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="C100" s="8">
         <v>247007.44</v>
@@ -2738,38 +2743,38 @@
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="101" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>200</v>
-      </c>
       <c r="C101" s="8">
-        <v>7499302.45</v>
+        <v>7499302.4500000002</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="102" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>202</v>
-      </c>
       <c r="C102" s="8">
-        <v>7871927.45</v>
+        <v>7871927.4500000002</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="103" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="7" t="s">
         <v>203</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>204</v>
       </c>
       <c r="C103" s="8">
         <v>229668</v>
@@ -2777,12 +2782,12 @@
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="104" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>206</v>
       </c>
       <c r="C104" s="8">
         <v>190080</v>
@@ -2790,12 +2795,12 @@
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="105" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="C105" s="8">
         <v>285120</v>
@@ -2803,12 +2808,12 @@
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="106" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="C106" s="8">
         <v>316800</v>
@@ -2816,12 +2821,12 @@
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="107" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="C107" s="8">
         <v>1235520</v>
@@ -2829,12 +2834,12 @@
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="108" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="C108" s="8">
         <v>582476.5</v>
@@ -2842,12 +2847,12 @@
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="109" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>216</v>
       </c>
       <c r="C109" s="8">
         <v>225720</v>
@@ -2855,12 +2860,12 @@
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="110" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B110" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="C110" s="8">
         <v>3120000</v>
@@ -2868,12 +2873,12 @@
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="111" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B111" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="C111" s="8">
         <v>570240</v>
@@ -2881,12 +2886,12 @@
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="112" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="C112" s="8">
         <v>285120</v>
@@ -2894,12 +2899,12 @@
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="113" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="C113" s="8">
         <v>855360</v>
@@ -2907,12 +2912,12 @@
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="114" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B114" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="C114" s="8">
         <v>190080</v>
@@ -2920,12 +2925,12 @@
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="115" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="C115" s="8">
         <v>285120</v>
@@ -2933,12 +2938,12 @@
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="116" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B116" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="C116" s="8">
         <v>855360</v>
@@ -2946,12 +2951,12 @@
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="117" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B117" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="C117" s="8">
         <v>855360</v>
@@ -2959,12 +2964,12 @@
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="15" customFormat="1" s="1">
+    <row r="118" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B118" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="C118" s="8">
         <v>855360</v>
@@ -2972,12 +2977,12 @@
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="119" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" s="7" t="s">
         <v>235</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>236</v>
       </c>
       <c r="C119" s="8">
         <v>570240</v>
@@ -2985,12 +2990,12 @@
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="120" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>237</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>238</v>
       </c>
       <c r="C120" s="8">
         <v>855360</v>
@@ -2998,12 +3003,12 @@
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="121" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" s="7" t="s">
         <v>239</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>240</v>
       </c>
       <c r="C121" s="8">
         <v>270000</v>
@@ -3011,12 +3016,12 @@
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="20.25" customFormat="1" s="1">
+    <row r="122" spans="1:5" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="C122" s="8">
         <v>112320</v>
@@ -3024,25 +3029,25 @@
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="123" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B123" s="7" t="s">
-        <v>244</v>
-      </c>
       <c r="C123" s="8">
-        <v>647971.55</v>
+        <v>647971.55000000005</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="124" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B124" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="C124" s="8">
         <v>5233480</v>
@@ -3050,12 +3055,12 @@
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="125" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B125" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="C125" s="8">
         <v>4548244.58</v>
@@ -3063,12 +3068,12 @@
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="126" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B126" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>250</v>
       </c>
       <c r="C126" s="8">
         <v>4164565.04</v>
@@ -3076,12 +3081,12 @@
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="127" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B127" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="C127" s="8">
         <v>187666.08</v>
@@ -3089,12 +3094,12 @@
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="128" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>254</v>
       </c>
       <c r="C128" s="8">
         <v>93833.04</v>
@@ -3102,12 +3107,12 @@
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="129" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="C129" s="8">
         <v>187666.08</v>
@@ -3115,12 +3120,12 @@
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="130" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B130" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="C130" s="8">
         <v>1313662.56</v>
@@ -3128,12 +3133,12 @@
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="131" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="C131" s="8">
         <v>281499.12</v>
@@ -3141,12 +3146,12 @@
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="132" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B132" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>262</v>
       </c>
       <c r="C132" s="8">
         <v>281499.12</v>
@@ -3154,12 +3159,12 @@
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="133" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B133" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="C133" s="8">
         <v>187666.08</v>
@@ -3167,12 +3172,12 @@
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="134" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B134" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="C134" s="8">
         <v>281499.12</v>
@@ -3180,12 +3185,12 @@
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="135" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>267</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>268</v>
       </c>
       <c r="C135" s="8">
         <v>93833.04</v>
@@ -3193,12 +3198,12 @@
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="136" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B136" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>270</v>
       </c>
       <c r="C136" s="8">
         <v>1162760</v>
@@ -3206,12 +3211,12 @@
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="137" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B137" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="C137" s="8">
         <v>450000</v>
@@ -3219,12 +3224,12 @@
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="21" customFormat="1" s="1">
+    <row r="138" spans="1:5" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>274</v>
       </c>
       <c r="C138" s="8">
         <v>4218890.28</v>
@@ -3232,12 +3237,12 @@
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="139" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B139" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>276</v>
       </c>
       <c r="C139" s="8">
         <v>7086500</v>
@@ -3245,12 +3250,12 @@
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="140" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B140" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="C140" s="8">
         <v>2418677.85</v>
@@ -3258,12 +3263,12 @@
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="141" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B141" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>280</v>
       </c>
       <c r="C141" s="8">
         <v>6517020</v>
@@ -3271,12 +3276,12 @@
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="142" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="C142" s="8">
         <v>998141.12</v>
@@ -3284,12 +3289,12 @@
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="143" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B143" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>284</v>
       </c>
       <c r="C143" s="8">
         <v>1235520</v>
@@ -3297,12 +3302,12 @@
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="144" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="C144" s="8">
         <v>994500</v>
@@ -3310,25 +3315,25 @@
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="145" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B145" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B145" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="C145" s="8">
-        <v>50992313.1</v>
+        <v>50992313.100000001</v>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="20.25" customFormat="1" s="1">
+    <row r="146" spans="1:5" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B146" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="C146" s="8">
         <v>90000</v>
@@ -3336,12 +3341,12 @@
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="147" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B147" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="C147" s="8">
         <v>528000</v>
@@ -3349,12 +3354,12 @@
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="20.25" customFormat="1" s="1">
+    <row r="148" spans="1:5" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B148" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>294</v>
       </c>
       <c r="C148" s="8">
         <v>320760</v>
@@ -3362,12 +3367,12 @@
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="149" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B149" s="7" t="s">
         <v>295</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>296</v>
       </c>
       <c r="C149" s="8">
         <v>476112.12</v>
@@ -3375,12 +3380,12 @@
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="150" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B150" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>298</v>
       </c>
       <c r="C150" s="8">
         <v>24400</v>
@@ -3388,12 +3393,12 @@
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="151" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B151" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>300</v>
       </c>
       <c r="C151" s="8">
         <v>286920</v>
@@ -3401,12 +3406,12 @@
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="152" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B152" s="7" t="s">
         <v>301</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>302</v>
       </c>
       <c r="C152" s="8">
         <v>450000</v>
@@ -3414,12 +3419,12 @@
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="153" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B153" s="7" t="s">
         <v>303</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>304</v>
       </c>
       <c r="C153" s="8">
         <v>200475</v>
@@ -3427,12 +3432,12 @@
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="154" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B154" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>306</v>
       </c>
       <c r="C154" s="8">
         <v>1648500</v>
@@ -3440,12 +3445,12 @@
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="155" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>307</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>308</v>
       </c>
       <c r="C155" s="8">
         <v>29073053.82</v>
@@ -3453,12 +3458,12 @@
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="15" customFormat="1" s="1">
+    <row r="156" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B156" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="C156" s="8">
         <v>16879440</v>
@@ -3466,12 +3471,12 @@
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="157" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B157" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="C157" s="8">
         <v>3462000</v>
@@ -3479,12 +3484,12 @@
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="158" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B158" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>314</v>
       </c>
       <c r="C158" s="8">
         <v>483750</v>
@@ -3492,12 +3497,12 @@
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="159" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B159" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>316</v>
       </c>
       <c r="C159" s="8">
         <v>1392900</v>
@@ -3505,12 +3510,12 @@
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="160" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B160" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>318</v>
       </c>
       <c r="C160" s="8">
         <v>748440</v>
@@ -3518,12 +3523,12 @@
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="161" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>320</v>
       </c>
       <c r="C161" s="8">
         <v>-26400</v>
@@ -3531,12 +3536,12 @@
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="14.25" customFormat="1" s="1">
+    <row r="162" spans="1:5" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>322</v>
       </c>
       <c r="C162" s="8">
         <v>-3</v>
